--- a/novo projeto/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-03).xlsx
+++ b/novo projeto/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-03).xlsx
@@ -935,10 +935,10 @@
     <t>214</t>
   </si>
   <si>
-    <t>23</t>
+    <t>22</t>
   </si>
   <si>
-    <t>R$ 4.558,40</t>
+    <t>R$ 4.554,43</t>
   </si>
   <si>
     <t>50.0</t>
@@ -959,7 +959,7 @@
     <t>6.4</t>
   </si>
   <si>
-    <t>43.2%</t>
+    <t>43.3%</t>
   </si>
   <si>
     <t>17.9%</t>
@@ -10169,7 +10169,7 @@
         <v>19618</v>
       </c>
       <c r="B58" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C58" s="4">
         <v>51</v>
@@ -10199,18 +10199,30 @@
         <v>58</v>
       </c>
       <c r="L58" s="4"/>
-      <c r="M58" s="5"/>
-      <c r="N58" s="6"/>
+      <c r="M58" s="5">
+        <v>3796.98</v>
+      </c>
+      <c r="N58" s="6">
+        <v>43</v>
+      </c>
       <c r="O58" s="6">
         <v>30</v>
       </c>
-      <c r="P58" s="7"/>
-      <c r="Q58" s="8"/>
-      <c r="R58" s="8"/>
+      <c r="P58" s="7">
+        <v>4.5898365853658536</v>
+      </c>
+      <c r="Q58" s="8">
+        <v>20.693333333333332</v>
+      </c>
+      <c r="R58" s="8">
+        <v>8.4355566666666668</v>
+      </c>
       <c r="S58" s="8">
         <v>7</v>
       </c>
-      <c r="T58" s="9"/>
+      <c r="T58" s="9">
+        <v>0.20000000000000001</v>
+      </c>
       <c r="U58" s="9">
         <v>0.066666666666666666</v>
       </c>
